--- a/my-web/Sample_Merchants.xlsx
+++ b/my-web/Sample_Merchants.xlsx
@@ -1,41 +1,406 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FOOD_AI_code\my-web\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB672CA8-2FDC-43D3-94DD-D46E5E0BF513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Merchants" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="123">
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Owner Name</t>
+  </si>
+  <si>
+    <t>Restaurant Name</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Restaurant Map URL</t>
+  </si>
+  <si>
+    <t>Food Name</t>
+  </si>
+  <si>
+    <t>Food Price</t>
+  </si>
+  <si>
+    <t>Food Desc</t>
+  </si>
+  <si>
+    <t>Food Image URL</t>
+  </si>
+  <si>
+    <t>Food Tags</t>
+  </si>
+  <si>
+    <t>Food line</t>
+  </si>
+  <si>
+    <t>phogiatruyen@gmail.com</t>
+  </si>
+  <si>
+    <t>password123</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Phở</t>
+  </si>
+  <si>
+    <t>Phở Gia Truyền Hà Nội</t>
+  </si>
+  <si>
+    <t>Đường Bưởi, Ba Đình, Hà Nội</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/JNVE8xJKFnMYtSYC9</t>
+  </si>
+  <si>
+    <t>Phở Bò Tái Nạm</t>
+  </si>
+  <si>
+    <t>Phở bò tái nạm thơm ngon, nước dùng ngọt thanh hầm từ xương bò 12 tiếng.</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1582878826629-29b7ad1cb431?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
+  </si>
+  <si>
+    <t>truyền thống,bữa sáng,bò</t>
+  </si>
+  <si>
+    <t>Phở Bò Chín</t>
+  </si>
+  <si>
+    <t>Thịt bò chín mềm, bánh phở dai ngon hòa quyện cùng nước dùng nóng hổi.</t>
+  </si>
+  <si>
+    <t>truyền thống,bò</t>
+  </si>
+  <si>
+    <t>Phở Gà Ta</t>
+  </si>
+  <si>
+    <t>Phở gà ta xé phay, da vàng giòn dai, nước dùng thanh tao.</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1601614285816-d8bb2cc36e26?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
+  </si>
+  <si>
+    <t>gà,truyền thống</t>
+  </si>
+  <si>
+    <t>Quẩy Nóng</t>
+  </si>
+  <si>
+    <t>Quẩy rán giòn rụm, ăn kèm với phở cực kì bắt miệng.</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1555939594-58d7cb561ad1?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
+  </si>
+  <si>
+    <t>ăn vặt,ăn kèm</t>
+  </si>
+  <si>
+    <t>banhmihoian@gmail.com</t>
+  </si>
+  <si>
+    <t>Trần Thị Mì</t>
+  </si>
+  <si>
+    <t>Bánh Mì Hội An 1990</t>
+  </si>
+  <si>
+    <t>Nguyễn Trãi, Thanh Xuân, Hà Nội</t>
+  </si>
+  <si>
+    <t>Bánh Mì Thập Cẩm</t>
+  </si>
+  <si>
+    <t>Bánh mì giòn rụm với pate, thịt xá xíu, chả lụa và sốt đặc biệt Hội An.</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1589302168068-964664d93dc0?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
+  </si>
+  <si>
+    <t>bánh mì,thịt heo,truyền thống</t>
+  </si>
+  <si>
+    <t>Bánh Mì Gà Quay</t>
+  </si>
+  <si>
+    <t>Thịt gà nướng xé nhỏ ngấm gia vị ăn cùng bánh mì giòn tan.</t>
+  </si>
+  <si>
+    <t>bánh mì,gà</t>
+  </si>
+  <si>
+    <t>Trà Tắc Khổng Lồ</t>
+  </si>
+  <si>
+    <t>Trà tắc chua ngọt mát lạnh, giải khát cực đã.</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1603569283847-aa295f0d016a?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
+  </si>
+  <si>
+    <t>đồ uống,giải khát,lạnh</t>
+  </si>
+  <si>
+    <t>comtamsg@gmail.com</t>
+  </si>
+  <si>
+    <t>Lê Văn Tấm</t>
+  </si>
+  <si>
+    <t>Cơm Tấm Sài Gòn Phố</t>
+  </si>
+  <si>
+    <t>Trần Duy Hưng, Cầu Giấy, Hà Nội</t>
+  </si>
+  <si>
+    <t>Cơm Tấm Sườn Bì Chả</t>
+  </si>
+  <si>
+    <t>Sườn nướng than hoa thơm lừng, bì dai giòn và chả trứng hấp dẫn.</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1623341214825-9f4f963727da?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
+  </si>
+  <si>
+    <t>cơm,thịt heo,truyền thống,bữa trưa</t>
+  </si>
+  <si>
+    <t>Cơm Tấm Sườn Trứng Ốp La</t>
+  </si>
+  <si>
+    <t>Cơm tấm sườn nướng kèm trứng ốp la lòng đào béo ngậy.</t>
+  </si>
+  <si>
+    <t>cơm,thịt heo,trứng</t>
+  </si>
+  <si>
+    <t>Cơm Gà Xối Mỡ</t>
+  </si>
+  <si>
+    <t>Đùi gà xối mỡ da giòn thịt mềm, ăn kèm cơm chiên đỏ và dưa chua.</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1579871494447-9811cf80d66c?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
+  </si>
+  <si>
+    <t>cơm,gà,đồ chiên</t>
+  </si>
+  <si>
+    <t>Canh Khổ Qua Nhồi Thịt</t>
+  </si>
+  <si>
+    <t>Canh khổ qua nấu nước hầm xương, thanh nhiệt giải độc.</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1546069901-ba9599a7e63c?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
+  </si>
+  <si>
+    <t>canh,thịt heo</t>
+  </si>
+  <si>
+    <t>pizzamaster@gmail.com</t>
+  </si>
+  <si>
+    <t>David Tran</t>
+  </si>
+  <si>
+    <t>Pizza Master &amp; Milktea</t>
+  </si>
+  <si>
+    <t>Tây Hồ, Hà Nội</t>
+  </si>
+  <si>
+    <t>Pizza Hải Sản (Cỡ Vừa)</t>
+  </si>
+  <si>
+    <t>Pizza hải sản tươi sống với phô mai mozzarella béo ngậy.</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1565299624946-b28f40a0ae38?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
+  </si>
+  <si>
+    <t>pizza,hải sản,phô mai,nhiều người</t>
+  </si>
+  <si>
+    <t>Pizza Xúc Xích Phô Mai</t>
+  </si>
+  <si>
+    <t>pizza,xúc xích,phô mai,ăn nhanh</t>
+  </si>
+  <si>
+    <t>Pizza xúc xích Đức kết hợp phô mai nướng chảy hấp dẫn mọi lứa tuổi.</t>
+  </si>
+  <si>
+    <t>Trà Sữa Trân Châu Đường Đen</t>
+  </si>
+  <si>
+    <t>Trà sữa đậm vị hồng trà quyện với trân châu đường đen dai giòn dẻo.</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1572490122747-3968b75cc699?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
+  </si>
+  <si>
+    <t>đồ uống,trà sữa,ngọt</t>
+  </si>
+  <si>
+    <t>Trà Sữa Kem Matcha</t>
+  </si>
+  <si>
+    <t>Trà sữa matcha xanh mướt với lớp kem macchiato mặn mặn béo ngậy.</t>
+  </si>
+  <si>
+    <t>đồ uống,trà sữa,matcha,lạnh</t>
+  </si>
+  <si>
+    <t>Pasta Sốt Kem Nấm</t>
+  </si>
+  <si>
+    <t>Mì Ý dai mềm cùng sốt kem tươi béo ngậy và nấm hương thơm lừng.</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1582450871972-ab5ce64f0f70?auto=format&amp;fit=crop&amp;w=800&amp;q=80</t>
+  </si>
+  <si>
+    <t>mì ý,pasta,kem</t>
+  </si>
+  <si>
+    <t>healthygreen@gmail.com</t>
+  </si>
+  <si>
+    <t>Phạm Thu Thủy</t>
+  </si>
+  <si>
+    <t>Healthy Green Bowl</t>
+  </si>
+  <si>
+    <t>Đống Đa, Hà Nội</t>
+  </si>
+  <si>
+    <t>Salad Cá Hồi</t>
+  </si>
+  <si>
+    <t>Salad rau xanh kết hợp cá hồi tươi áp chảo và nước sốt mè rang.</t>
+  </si>
+  <si>
+    <t>healthy,cá hồi,salad,eat clean</t>
+  </si>
+  <si>
+    <t>Salad Lườn Gà</t>
+  </si>
+  <si>
+    <t>Thịt lườn gà xé nhỏ trộn cùng xà lách, cà chua bi và sốt chua ngọt.</t>
+  </si>
+  <si>
+    <t>healthy,gà,salad,giảm cân</t>
+  </si>
+  <si>
+    <t>Cơm Gạo Lứt Bò Lúc Lắc</t>
+  </si>
+  <si>
+    <t>Cơm gạo lứt ăn kèm bò lúc lắc xào ớt chuông dinh dưỡng.</t>
+  </si>
+  <si>
+    <t>healthy,bò,cơm gạo lứt</t>
+  </si>
+  <si>
+    <t>Nước Ép Cần Tây Táo</t>
+  </si>
+  <si>
+    <t>Nước ép detox tươi mát, thanh lọc cơ thể, giữ dáng đẹp da.</t>
+  </si>
+  <si>
+    <t>đồ uống,healthy,nước ép</t>
+  </si>
+  <si>
+    <t>quannhauboke@gmail.com</t>
+  </si>
+  <si>
+    <t>Bùi Văn Kè</t>
+  </si>
+  <si>
+    <t>Bờ Kè Quán Nhậu</t>
+  </si>
+  <si>
+    <t>Hoàng Cầu, Hà Nội</t>
+  </si>
+  <si>
+    <t>Lẩu Gà Lá É</t>
+  </si>
+  <si>
+    <t>Lẩu gà ta Phú Yên trứ danh với lá é thơm lừng, chua cay nhẹ.</t>
+  </si>
+  <si>
+    <t>lẩu,gà,nhậu,nhiều người</t>
+  </si>
+  <si>
+    <t>Mực Nướng Sa Tế</t>
+  </si>
+  <si>
+    <t>Mực nang tươi nướng sa tế cay xé lưỡi, mồi nhậu cực bén.</t>
+  </si>
+  <si>
+    <t>hải sản,đồ nướng,cay,nhậu</t>
+  </si>
+  <si>
+    <t>Bò Nhúng Dấm</t>
+  </si>
+  <si>
+    <t>Thịt bò tươi nhúng nước dấm chua ngọt, cuốn bánh tráng rau sống.</t>
+  </si>
+  <si>
+    <t>bò,cuốn,nhậu</t>
+  </si>
+  <si>
+    <t>Bia Hơi Hà Nội (Cốc)</t>
+  </si>
+  <si>
+    <t>Bia hơi truyền thống giải nhiệt mùa hè, chuẩn vị quán nhậu.</t>
+  </si>
+  <si>
+    <t>đồ uống,bia,nhậu,lạnh</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,6 +437,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,126 +769,1045 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="40.3984375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Email</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Password</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Owner Name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Restaurant Name</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Address</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Latitude</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Longitude</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Food Name</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Food Price</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Food Desc</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Food Image URL</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Food Tags</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>merchant@test.com</v>
-      </c>
-      <c r="B2" t="str">
-        <v>password123</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Nguyen Van A</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Phở Hà Nội</v>
-      </c>
-      <c r="E2" t="str">
-        <v>123 Đường B, Quận C, TP HCM</v>
+    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>10.762622</v>
+        <v>20.974366</v>
       </c>
       <c r="G2">
-        <v>106.660172</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Phở Bò</v>
-      </c>
-      <c r="I2">
+        <v>105.7574331</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2">
         <v>50000</v>
       </c>
-      <c r="J2" t="str">
-        <v>Phở bò tái nạm</v>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v>Phở, Bò, Sáng</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>merchant@test.com</v>
-      </c>
-      <c r="B3" t="str">
-        <v>password123</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Nguyen Van A</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Phở Hà Nội</v>
-      </c>
-      <c r="E3" t="str">
-        <v>123 Đường B, Quận C, TP HCM</v>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>10.762622</v>
+        <v>20.974366</v>
       </c>
       <c r="G3">
-        <v>106.660172</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Phở Gà</v>
-      </c>
-      <c r="I3">
+        <v>105.7574331</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3">
         <v>45000</v>
       </c>
-      <c r="J3" t="str">
-        <v>Phở gà ta</v>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>Phở, Gà, Sáng</v>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>20.974366</v>
+      </c>
+      <c r="G4">
+        <v>105.7574331</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4">
+        <v>40000</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>20.974366</v>
+      </c>
+      <c r="G5">
+        <v>105.7574331</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5">
+        <v>5000</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6">
+        <v>20.974366</v>
+      </c>
+      <c r="G6">
+        <v>105.7574331</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6">
+        <v>35000</v>
+      </c>
+      <c r="K6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>20.974366</v>
+      </c>
+      <c r="G7">
+        <v>105.7574331</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7">
+        <v>30000</v>
+      </c>
+      <c r="K7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8">
+        <v>20.974366</v>
+      </c>
+      <c r="G8">
+        <v>105.7574331</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8">
+        <v>15000</v>
+      </c>
+      <c r="K8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9">
+        <v>20.974366</v>
+      </c>
+      <c r="G9">
+        <v>105.7574331</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9">
+        <v>65000</v>
+      </c>
+      <c r="K9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10">
+        <v>20.974366</v>
+      </c>
+      <c r="G10">
+        <v>105.7574331</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10">
+        <v>60000</v>
+      </c>
+      <c r="K10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11">
+        <v>20.974366</v>
+      </c>
+      <c r="G11">
+        <v>105.7574331</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11">
+        <v>55000</v>
+      </c>
+      <c r="K11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12">
+        <v>20.974366</v>
+      </c>
+      <c r="G12">
+        <v>105.7574331</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12">
+        <v>20000</v>
+      </c>
+      <c r="K12" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" t="s">
+        <v>67</v>
+      </c>
+      <c r="M12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13">
+        <v>20.974366</v>
+      </c>
+      <c r="G13">
+        <v>105.7574331</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" t="s">
+        <v>73</v>
+      </c>
+      <c r="J13">
+        <v>149000</v>
+      </c>
+      <c r="K13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L13" t="s">
+        <v>75</v>
+      </c>
+      <c r="M13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14">
+        <v>20.974366</v>
+      </c>
+      <c r="G14">
+        <v>105.7574331</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s">
+        <v>77</v>
+      </c>
+      <c r="J14">
+        <v>129000</v>
+      </c>
+      <c r="L14" t="s">
+        <v>75</v>
+      </c>
+      <c r="M14" t="s">
+        <v>78</v>
+      </c>
+      <c r="N14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15">
+        <v>20.974366</v>
+      </c>
+      <c r="G15">
+        <v>105.7574331</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15">
+        <v>45000</v>
+      </c>
+      <c r="K15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L15" t="s">
+        <v>82</v>
+      </c>
+      <c r="M15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16">
+        <v>20.974366</v>
+      </c>
+      <c r="G16">
+        <v>105.7574331</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" t="s">
+        <v>84</v>
+      </c>
+      <c r="J16">
+        <v>50000</v>
+      </c>
+      <c r="K16" t="s">
+        <v>85</v>
+      </c>
+      <c r="L16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17">
+        <v>20.974366</v>
+      </c>
+      <c r="G17">
+        <v>105.7574331</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" t="s">
+        <v>87</v>
+      </c>
+      <c r="J17">
+        <v>85000</v>
+      </c>
+      <c r="K17" t="s">
+        <v>88</v>
+      </c>
+      <c r="L17" t="s">
+        <v>89</v>
+      </c>
+      <c r="M17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18">
+        <v>20.974366</v>
+      </c>
+      <c r="G18">
+        <v>105.7574331</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" t="s">
+        <v>95</v>
+      </c>
+      <c r="J18">
+        <v>85000</v>
+      </c>
+      <c r="K18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L18" t="s">
+        <v>67</v>
+      </c>
+      <c r="M18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19">
+        <v>20.974366</v>
+      </c>
+      <c r="G19">
+        <v>105.7574331</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s">
+        <v>98</v>
+      </c>
+      <c r="J19">
+        <v>65000</v>
+      </c>
+      <c r="K19" t="s">
+        <v>99</v>
+      </c>
+      <c r="L19" t="s">
+        <v>67</v>
+      </c>
+      <c r="M19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20">
+        <v>20.974366</v>
+      </c>
+      <c r="G20">
+        <v>105.7574331</v>
+      </c>
+      <c r="H20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" t="s">
+        <v>101</v>
+      </c>
+      <c r="J20">
+        <v>95000</v>
+      </c>
+      <c r="K20" t="s">
+        <v>102</v>
+      </c>
+      <c r="L20" t="s">
+        <v>63</v>
+      </c>
+      <c r="M20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21">
+        <v>20.974366</v>
+      </c>
+      <c r="G21">
+        <v>105.7574331</v>
+      </c>
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" t="s">
+        <v>104</v>
+      </c>
+      <c r="J21">
+        <v>40000</v>
+      </c>
+      <c r="K21" t="s">
+        <v>105</v>
+      </c>
+      <c r="L21" t="s">
+        <v>48</v>
+      </c>
+      <c r="M21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22">
+        <v>20.974366</v>
+      </c>
+      <c r="G22">
+        <v>105.7574331</v>
+      </c>
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" t="s">
+        <v>111</v>
+      </c>
+      <c r="J22">
+        <v>250000</v>
+      </c>
+      <c r="K22" t="s">
+        <v>112</v>
+      </c>
+      <c r="L22" t="s">
+        <v>22</v>
+      </c>
+      <c r="M22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" t="s">
+        <v>110</v>
+      </c>
+      <c r="F23">
+        <v>20.974366</v>
+      </c>
+      <c r="G23">
+        <v>105.7574331</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J23">
+        <v>120000</v>
+      </c>
+      <c r="K23" t="s">
+        <v>115</v>
+      </c>
+      <c r="L23" t="s">
+        <v>33</v>
+      </c>
+      <c r="M23" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24">
+        <v>20.974366</v>
+      </c>
+      <c r="G24">
+        <v>105.7574331</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" t="s">
+        <v>117</v>
+      </c>
+      <c r="J24">
+        <v>200000</v>
+      </c>
+      <c r="K24" t="s">
+        <v>118</v>
+      </c>
+      <c r="L24" t="s">
+        <v>29</v>
+      </c>
+      <c r="M24" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25">
+        <v>20.974366</v>
+      </c>
+      <c r="G25">
+        <v>105.7574331</v>
+      </c>
+      <c r="H25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" t="s">
+        <v>120</v>
+      </c>
+      <c r="J25">
+        <v>12000</v>
+      </c>
+      <c r="K25" t="s">
+        <v>121</v>
+      </c>
+      <c r="L25" t="s">
+        <v>48</v>
+      </c>
+      <c r="M25" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError sqref="A1:N25" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>